--- a/src/main/java/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
@@ -1,42 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6969066-96AB-4820-A30F-1BABC7517B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B49A7E6-374D-4FD0-88FB-3915D8CCABAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{92F47CF0-95F9-4D84-814C-7AFFA20164B6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{92F47CF0-95F9-4D84-814C-7AFFA20164B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="38">
   <si>
     <t>CODIGO</t>
   </si>
@@ -144,6 +136,12 @@
   </si>
   <si>
     <t>Papel bond tamaño carta 75g</t>
+  </si>
+  <si>
+    <t>MONI01</t>
+  </si>
+  <si>
+    <t>Monitor LED 21.5 pulgadas HP</t>
   </si>
 </sst>
 </file>
@@ -151,7 +149,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -522,13 +520,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1658ADDC-DCFD-4FC0-A51D-94B360144F05}">
-  <dimension ref="A1:G44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.36328125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -551,9 +549,101 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1771.62</v>
+      </c>
+      <c r="G2">
+        <v>1771.62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G3">
+        <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G4">
+        <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G5">
+        <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -574,15 +664,15 @@
         <v>1771.62</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7">
       <c r="A7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
@@ -597,9 +687,9 @@
         <v>2137.5100000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7">
       <c r="A8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -620,15 +710,15 @@
         <v>2137.5100000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7">
       <c r="A9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
@@ -637,38 +727,38 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>2137.5100000000002</v>
+        <v>580</v>
       </c>
       <c r="G9">
-        <v>2137.5100000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>1771.62</v>
+        <v>205.6</v>
       </c>
       <c r="G10">
-        <v>1771.62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>205.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -689,124 +779,331 @@
         <v>2137.5100000000002</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>6.0</v>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>180</v>
+      </c>
+      <c r="G12">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1771.62</v>
+      </c>
+      <c r="G13">
+        <v>1771.62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G14">
+        <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G15">
+        <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G16">
+        <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>95.5</v>
+      </c>
+      <c r="G17">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>180</v>
+      </c>
+      <c r="G18">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>210.75</v>
+      </c>
+      <c r="G19">
+        <v>210.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20">
+        <v>8</v>
+      </c>
+      <c r="F20">
+        <v>95</v>
+      </c>
+      <c r="G20">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
         <v>9</v>
       </c>
-      <c r="E21" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>6.0</v>
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="F21">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G21">
+        <v>8550.0400000000009</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>580.0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>580.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>6.0</v>
+        <v>20</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>110.25</v>
+      </c>
+      <c r="G22">
+        <v>110.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23">
+        <v>5</v>
+      </c>
+      <c r="F23">
+        <v>780</v>
+      </c>
+      <c r="G23">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" t="s">
         <v>25</v>
       </c>
-      <c r="E23" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>205.6</v>
-      </c>
-      <c r="G23" t="n">
-        <v>205.6</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="B24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>6.0</v>
+      <c r="E24">
+        <v>34</v>
+      </c>
+      <c r="F24">
+        <v>210.75</v>
+      </c>
+      <c r="G24">
+        <v>7165.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
         <v>9</v>
       </c>
-      <c r="E25" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>180.0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>180.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>7.0</v>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>310</v>
+      </c>
+      <c r="G25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>4</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
@@ -817,428 +1114,221 @@
       <c r="D26" t="s">
         <v>9</v>
       </c>
-      <c r="E26" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F26" t="n">
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
         <v>1771.62</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>1771.62</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>7.0</v>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>4</v>
       </c>
       <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G27">
+        <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G28">
+        <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1771.62</v>
+      </c>
+      <c r="G29">
+        <v>1771.62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
         <v>10</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C30" t="s">
         <v>11</v>
       </c>
-      <c r="D27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="B28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G30">
+        <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
         <v>14</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C31" t="s">
         <v>15</v>
       </c>
-      <c r="D29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="B30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="G30" t="n">
-        <v>95.5</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="B31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" t="s">
-        <v>33</v>
-      </c>
       <c r="D31" t="s">
         <v>9</v>
       </c>
-      <c r="E31" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>180.0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>180.0</v>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G31">
+        <v>2137.5100000000002</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
         <v>1.0</v>
       </c>
       <c r="F32" t="n">
-        <v>210.75</v>
+        <v>2137.51</v>
       </c>
       <c r="G32" t="n">
-        <v>210.75</v>
+        <v>2137.51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s">
         <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="F33" t="n">
-        <v>95.0</v>
+        <v>180.0</v>
       </c>
       <c r="G33" t="n">
-        <v>760.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="F34" t="n">
-        <v>2137.51</v>
+        <v>2850.0</v>
       </c>
       <c r="G34" t="n">
-        <v>8550.04</v>
+        <v>2850.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E35" t="n">
         <v>1.0</v>
       </c>
       <c r="F35" t="n">
-        <v>110.25</v>
+        <v>210.75</v>
       </c>
       <c r="G35" t="n">
-        <v>110.25</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B36" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" t="s">
-        <v>22</v>
-      </c>
-      <c r="D36" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>780.0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>3900.0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B37" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" t="n">
-        <v>34.0</v>
-      </c>
-      <c r="F37" t="n">
         <v>210.75</v>
-      </c>
-      <c r="G37" t="n">
-        <v>7165.5</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B38" t="s">
-        <v>26</v>
-      </c>
-      <c r="C38" t="s">
-        <v>27</v>
-      </c>
-      <c r="D38" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>310.0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>310.0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1771.62</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1771.62</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B41" t="s">
-        <v>14</v>
-      </c>
-      <c r="C41" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="B42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1771.62</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1771.62</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="B43" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="B44" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G44" t="n">
-        <v>2137.51</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="40">
   <si>
     <t>CODIGO</t>
   </si>
@@ -142,6 +142,12 @@
   </si>
   <si>
     <t>Monitor LED 21.5 pulgadas HP</t>
+  </si>
+  <si>
+    <t>DISC01</t>
+  </si>
+  <si>
+    <t>Disco duro externo 1TB Seagate</t>
   </si>
 </sst>
 </file>
@@ -520,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1658ADDC-DCFD-4FC0-A51D-94B360144F05}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" bestFit="true" customWidth="true" width="12.375" collapsed="true"/>
@@ -1331,6 +1337,98 @@
         <v>210.75</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1250.0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>37500.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>580.0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>580.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>310.0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/java/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="57">
   <si>
     <t>CODIGO</t>
   </si>
@@ -148,6 +148,57 @@
   </si>
   <si>
     <t>Disco duro externo 1TB Seagate</t>
+  </si>
+  <si>
+    <t>EPSON03</t>
+  </si>
+  <si>
+    <t>Tinta Epson 544 Magenta</t>
+  </si>
+  <si>
+    <t>USB001</t>
+  </si>
+  <si>
+    <t>Memoria USB 32GB Kingston</t>
+  </si>
+  <si>
+    <t>MOUSE01</t>
+  </si>
+  <si>
+    <t>Mouse óptico inalámbrico Logitech</t>
+  </si>
+  <si>
+    <t>CAN001</t>
+  </si>
+  <si>
+    <t>Cartucho Canon CL-211 Color</t>
+  </si>
+  <si>
+    <t>CARBOL-01</t>
+  </si>
+  <si>
+    <t>Cartucho de tinta original color negro para impresoras de inyección, diseñado para ofrecer impresiones nítidas y rendimiento confiable</t>
+  </si>
+  <si>
+    <t>SILLAERG-01</t>
+  </si>
+  <si>
+    <t>Silla ejecutiva ergonómica con respaldo alto, asiento acolchado, descansabrazos y mecanismo de ajuste de altura para jornadas prolongadas de trabajo</t>
+  </si>
+  <si>
+    <t>LIMP500</t>
+  </si>
+  <si>
+    <t>Limpiador líquido multiusos de 500 ml para superficies de oficina, formulado para remover polvo, grasa ligera y suciedad cotidiana</t>
+  </si>
+  <si>
+    <t>GRAP26-5000</t>
+  </si>
+  <si>
+    <t>Caja con 5000 grapas estándar calibre 26/6, fabricadas para engrapadoras de oficina y uso frecuente en documentos de diferentes grosores</t>
+  </si>
+  <si>
+    <t>CJA</t>
   </si>
 </sst>
 </file>
@@ -526,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1658ADDC-DCFD-4FC0-A51D-94B360144F05}">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" bestFit="true" customWidth="true" width="12.375" collapsed="true"/>
@@ -693,121 +744,6 @@
         <v>2137.5100000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>2137.5100000000002</v>
-      </c>
-      <c r="G8">
-        <v>2137.5100000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>580</v>
-      </c>
-      <c r="G9">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>205.6</v>
-      </c>
-      <c r="G10">
-        <v>205.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>2137.5100000000002</v>
-      </c>
-      <c r="G11">
-        <v>2137.5100000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>180</v>
-      </c>
-      <c r="G12">
-        <v>180</v>
-      </c>
-    </row>
     <row r="13" spans="1:7">
       <c r="A13">
         <v>7</v>
@@ -1427,6 +1363,581 @@
       </c>
       <c r="G39" t="n">
         <v>2137.51</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>580.0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>580.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" t="s">
+        <v>31</v>
+      </c>
+      <c r="D50" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="G50" t="n">
+        <v>205.6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" t="s">
+        <v>33</v>
+      </c>
+      <c r="D52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>180.0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>180.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1771.62</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1771.62</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="G55" t="n">
+        <v>205.6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57" t="s">
+        <v>41</v>
+      </c>
+      <c r="D57" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="G57" t="n">
+        <v>205.6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>42</v>
+      </c>
+      <c r="C58" t="s">
+        <v>43</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>120.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>23</v>
+      </c>
+      <c r="C59" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>210.75</v>
+      </c>
+      <c r="G59" t="n">
+        <v>210.75</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" t="s">
+        <v>33</v>
+      </c>
+      <c r="D60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>180.0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>180.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>44</v>
+      </c>
+      <c r="C61" t="s">
+        <v>45</v>
+      </c>
+      <c r="D61" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>220.0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>220.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B62" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62" t="s">
+        <v>35</v>
+      </c>
+      <c r="D62" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B63" t="s">
+        <v>36</v>
+      </c>
+      <c r="C63" t="s">
+        <v>37</v>
+      </c>
+      <c r="D63" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2850.0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2850.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B64" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1771.62</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1771.62</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B65" t="s">
+        <v>42</v>
+      </c>
+      <c r="C65" t="s">
+        <v>43</v>
+      </c>
+      <c r="D65" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>120.0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B66" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B68" t="s">
+        <v>46</v>
+      </c>
+      <c r="C68" t="s">
+        <v>47</v>
+      </c>
+      <c r="D68" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>620.0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>620.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B69" t="s">
+        <v>48</v>
+      </c>
+      <c r="C69" t="s">
+        <v>49</v>
+      </c>
+      <c r="D69" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>524.7</v>
+      </c>
+      <c r="G69" t="n">
+        <v>524.7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B70" t="s">
+        <v>50</v>
+      </c>
+      <c r="C70" t="s">
+        <v>51</v>
+      </c>
+      <c r="D70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3249.0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3249.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B71" t="s">
+        <v>52</v>
+      </c>
+      <c r="C71" t="s">
+        <v>53</v>
+      </c>
+      <c r="D71" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>86.9</v>
+      </c>
+      <c r="G71" t="n">
+        <v>86.9</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B72" t="s">
+        <v>54</v>
+      </c>
+      <c r="C72" t="s">
+        <v>55</v>
+      </c>
+      <c r="D72" t="s">
+        <v>56</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="G72" t="n">
+        <v>63.25</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="61">
   <si>
     <t>CODIGO</t>
   </si>
@@ -199,6 +199,18 @@
   </si>
   <si>
     <t>CJA</t>
+  </si>
+  <si>
+    <t>CANTIDAD_RECIBIDA</t>
+  </si>
+  <si>
+    <t>PENDIENTE_RECIBIR</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -577,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1658ADDC-DCFD-4FC0-A51D-94B360144F05}">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" bestFit="true" customWidth="true" width="12.375" collapsed="true"/>
@@ -605,6 +617,12 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
@@ -628,6 +646,12 @@
       <c r="G2">
         <v>1771.62</v>
       </c>
+      <c r="H2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I2" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
@@ -651,6 +675,12 @@
       <c r="G3">
         <v>2137.5100000000002</v>
       </c>
+      <c r="H3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
@@ -674,6 +704,12 @@
       <c r="G4">
         <v>2137.5100000000002</v>
       </c>
+      <c r="H4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
@@ -697,6 +733,12 @@
       <c r="G5">
         <v>2137.5100000000002</v>
       </c>
+      <c r="H5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
@@ -836,75 +878,6 @@
         <v>2137.5100000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>8</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>95.5</v>
-      </c>
-      <c r="G17">
-        <v>95.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>8</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <v>180</v>
-      </c>
-      <c r="G18">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>8</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19">
-        <v>210.75</v>
-      </c>
-      <c r="G19">
-        <v>210.75</v>
-      </c>
-    </row>
     <row r="20" spans="1:7">
       <c r="A20">
         <v>5</v>
@@ -1938,6 +1911,75 @@
       </c>
       <c r="G72" t="n">
         <v>63.25</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B73" t="s">
+        <v>34</v>
+      </c>
+      <c r="C73" t="s">
+        <v>35</v>
+      </c>
+      <c r="D73" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="G73" t="n">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B74" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" t="s">
+        <v>33</v>
+      </c>
+      <c r="D74" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>180.0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>180.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B75" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" t="s">
+        <v>24</v>
+      </c>
+      <c r="D75" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>210.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>210.75</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="50">
   <si>
     <t>CODIGO</t>
   </si>
@@ -559,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1658ADDC-DCFD-4FC0-A51D-94B360144F05}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="3" max="3" bestFit="true" customWidth="true" width="12.3984375" collapsed="true"/>
@@ -1461,6 +1461,213 @@
         <v>205.6</v>
       </c>
       <c r="G33" t="n">
+        <v>205.6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="G38" t="n">
+        <v>110.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>620.0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>620.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>580.0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>580.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>210.75</v>
+      </c>
+      <c r="G41" t="n">
+        <v>210.75</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="G42" t="n">
         <v>205.6</v>
       </c>
     </row>

--- a/src/main/java/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1469F88E-8890-4A4B-8C45-328973A14366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28715A0-6E48-45E3-8C06-4DD9B861EEF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3024" yWindow="2304" windowWidth="16740" windowHeight="9372" xr2:uid="{92F47CF0-95F9-4D84-814C-7AFFA20164B6}"/>
+    <workbookView xWindow="612" yWindow="-108" windowWidth="22536" windowHeight="13176" xr2:uid="{92F47CF0-95F9-4D84-814C-7AFFA20164B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$I$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$I$52</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="44">
   <si>
     <t>CODIGO</t>
   </si>
@@ -57,15 +57,54 @@
     <t>PENDIENTE_RECIBIR</t>
   </si>
   <si>
+    <t>MOU8200</t>
+  </si>
+  <si>
+    <t>Mouse óptico inalámbrico de tres botones con sensor de alta precisión, diseño compacto y receptor USB para equipos de escritorio y portátiles</t>
+  </si>
+  <si>
+    <t>PZA</t>
+  </si>
+  <si>
+    <t>PAPBOND75</t>
+  </si>
+  <si>
+    <t>Papel bond blanco tamaño carta de 75 gramos, paquete de alta blancura para impresión y copiado cotidiano de documentos administrativos</t>
+  </si>
+  <si>
+    <t>PAQ</t>
+  </si>
+  <si>
+    <t>REG1200</t>
+  </si>
+  <si>
+    <t>Regulador electrónico de voltaje de 1200 VA con protección contra variaciones eléctricas y múltiples contactos para equipos de cómputo</t>
+  </si>
+  <si>
+    <t>LIMP500</t>
+  </si>
+  <si>
+    <t>Limpiador líquido multiusos de 500 ml para superficies de oficina, formulado para remover polvo, grasa ligera y suciedad cotidiana</t>
+  </si>
+  <si>
+    <t>EXT6-10M</t>
+  </si>
+  <si>
+    <t>Extensión eléctrica de 10 metros con cable reforzado, clavija polarizada y contactos múltiples para conectar equipos y accesorios en áreas de trabajo</t>
+  </si>
+  <si>
+    <t>W2300A</t>
+  </si>
+  <si>
+    <t>Tóner original W2300A Negro</t>
+  </si>
+  <si>
     <t>W2301A</t>
   </si>
   <si>
     <t>Tóner original W2300A Cian</t>
   </si>
   <si>
-    <t>PZA</t>
-  </si>
-  <si>
     <t>W2302A</t>
   </si>
   <si>
@@ -84,37 +123,43 @@
     <t>Papel bond tamaño carta 75g</t>
   </si>
   <si>
-    <t>PAQ</t>
-  </si>
-  <si>
     <t>HP1021</t>
   </si>
   <si>
     <t>Papel bond tamaño oficio 75g</t>
   </si>
   <si>
+    <t>CAN002</t>
+  </si>
+  <si>
+    <t>Cartucho Canon PG-210 Negro</t>
+  </si>
+  <si>
+    <t>EPSON01</t>
+  </si>
+  <si>
+    <t>Tinta Epson 544 Negro</t>
+  </si>
+  <si>
+    <t>ML</t>
+  </si>
+  <si>
+    <t>EPSON02</t>
+  </si>
+  <si>
+    <t>Tinta Epson 544 Cian</t>
+  </si>
+  <si>
+    <t>EPSON03</t>
+  </si>
+  <si>
+    <t>Tinta Epson 544 Magenta</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>W2300A</t>
-  </si>
-  <si>
-    <t>Tóner original W2300A Negro</t>
   </si>
 </sst>
 </file>
@@ -493,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1658ADDC-DCFD-4FC0-A51D-94B360144F05}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" bestFit="true" customWidth="true" width="12.44140625" collapsed="true"/>
@@ -547,16 +592,16 @@
         <v>1.0</v>
       </c>
       <c r="F2" t="n">
-        <v>2137.51</v>
+        <v>289.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2137.51</v>
+        <v>289.5</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -570,22 +615,22 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F3" t="n">
-        <v>2137.51</v>
+        <v>118.6</v>
       </c>
       <c r="G3" t="n">
-        <v>4275.02</v>
+        <v>118.6</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -593,28 +638,28 @@
         <v>1.0</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="F4" t="n">
-        <v>2137.51</v>
+        <v>895.25</v>
       </c>
       <c r="G4" t="n">
-        <v>12825.060000000001</v>
+        <v>895.25</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -622,28 +667,28 @@
         <v>1.0</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="F5" t="n">
-        <v>95.5</v>
+        <v>86.9</v>
       </c>
       <c r="G5" t="n">
-        <v>382.0</v>
+        <v>86.9</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="I5" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -657,33 +702,33 @@
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>1.0</v>
       </c>
       <c r="F6" t="n">
-        <v>110.25</v>
+        <v>349.9</v>
       </c>
       <c r="G6" t="n">
-        <v>110.25</v>
+        <v>349.9</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="I6" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -692,172 +737,172 @@
         <v>1.0</v>
       </c>
       <c r="F7" t="n">
-        <v>2137.51</v>
+        <v>1771.62</v>
       </c>
       <c r="G7" t="n">
-        <v>2137.51</v>
+        <v>1771.62</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="I7" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F8" t="n">
         <v>2137.51</v>
       </c>
       <c r="G8" t="n">
-        <v>4275.02</v>
+        <v>2137.51</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="I8" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="F9" t="n">
         <v>2137.51</v>
       </c>
       <c r="G9" t="n">
-        <v>12825.060000000001</v>
+        <v>2137.51</v>
       </c>
       <c r="H9" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I9" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="F10" t="n">
-        <v>95.5</v>
+        <v>2137.51</v>
       </c>
       <c r="G10" t="n">
-        <v>382.0</v>
+        <v>2137.51</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="I10" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
         <v>1.0</v>
       </c>
       <c r="F11" t="n">
-        <v>110.25</v>
+        <v>95.5</v>
       </c>
       <c r="G11" t="n">
-        <v>110.25</v>
+        <v>95.5</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="I11" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
         <v>1.0</v>
       </c>
       <c r="F12" t="n">
-        <v>1771.62</v>
+        <v>110.25</v>
       </c>
       <c r="G12" t="n">
-        <v>1771.62</v>
+        <v>110.25</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="I12" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -866,80 +911,385 @@
         <v>1.0</v>
       </c>
       <c r="F13" t="n">
-        <v>2137.51</v>
+        <v>580.0</v>
       </c>
       <c r="G13" t="n">
-        <v>2137.51</v>
+        <v>580.0</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="I13" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E14" t="n">
         <v>1.0</v>
       </c>
       <c r="F14" t="n">
-        <v>2137.51</v>
+        <v>210.75</v>
       </c>
       <c r="G14" t="n">
-        <v>2137.51</v>
+        <v>210.75</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="I14" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="H15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="H16" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
         <v>14</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>118.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B18" t="s">
         <v>15</v>
       </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>895.25</v>
+      </c>
+      <c r="G18" t="n">
+        <v>895.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>86.9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>86.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>349.9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>349.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1771.62</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1771.62</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F22" t="n">
         <v>2137.51</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G22" t="n">
         <v>2137.51</v>
       </c>
-      <c r="H15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" t="s">
-        <v>22</v>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9550.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>580.0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>580.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>210.75</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1053.75</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>205.6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I80" xr:uid="{7D811ECF-302C-4453-AA90-921548F2E119}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I80">
-      <sortCondition ref="A1:A80"/>
+  <autoFilter ref="A1:I52" xr:uid="{7D811ECF-302C-4453-AA90-921548F2E119}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I52">
+      <sortCondition ref="A1:A52"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
